--- a/recipes/onion-garlic-free-indian/focus-states/04-west-bengal/excel/west-bengal-recipes.xlsx
+++ b/recipes/onion-garlic-free-indian/focus-states/04-west-bengal/excel/west-bengal-recipes.xlsx
@@ -104,7 +104,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="009A3412"/>
-      <sz val="16"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="19">
@@ -259,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -358,6 +358,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1465,7 +1468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1477,7 +1480,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Aloo Posto</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Aloo Posto</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1487,7 +1490,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>West Bengal kitchen  ·  Side  ·  Bengali niramish (vegetarian, no onion garlic)</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  West Bengal  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1507,44 +1510,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 10 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -1764,38 +1767,217 @@
       <c r="C23" s="46" t="n"/>
       <c r="D23" s="46" t="n"/>
     </row>
-    <row r="24" ht="36" customHeight="1">
+    <row r="24" ht="66" customHeight="1">
       <c r="A24" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B24" s="48" t="inlineStr">
         <is>
-          <t>Cook potatoes, add posto. Oil should shine. No peyaj, no rasun.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C24" s="49" t="n"/>
       <c r="D24" s="49" t="n"/>
     </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. If using potato, cook until tender, drain, and steam-dry so the mix is not wet.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Cook potatoes, add posto. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Oil should shine. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>No peyaj, no rasun. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="31" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="22" t="n"/>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>kcal 151  ·  Protein 2 g  ·  Carbs 19 g  ·  Fat 7 g  ·  Fibre 3 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="48" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="72" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>For Aloo Posto: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B39" s="52" t="n"/>
+      <c r="C39" s="52" t="n"/>
+      <c r="D39" s="52" t="n"/>
+    </row>
+    <row r="40" ht="64" customHeight="1">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B40" s="50" t="n"/>
+      <c r="C40" s="50" t="n"/>
+      <c r="D40" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="C20:D20"/>
+  <mergeCells count="33">
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A33:D33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -1809,7 +1991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1821,7 +2003,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Labra</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Labra</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1831,7 +2013,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>West Bengal kitchen  ·  Side  ·  Bengali niramish (vegetarian, no onion garlic)</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  West Bengal  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1851,44 +2033,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 15 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -2090,37 +2272,203 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Temper, add veg, cook until they melt together. Bhog style.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="66" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Temper, add veg, cook until they melt together. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Bhog style. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 184  ·  Protein 1 g  ·  Carbs 31 g  ·  Fat 7 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Labra: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2134,7 +2482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2146,7 +2494,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Lau Ghonto</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Lau Ghonto</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2156,7 +2504,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>West Bengal kitchen  ·  Side  ·  Bengali niramish (vegetarian, no onion garlic)</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  West Bengal  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2176,44 +2524,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 10 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -2433,38 +2781,191 @@
       <c r="C23" s="46" t="n"/>
       <c r="D23" s="46" t="n"/>
     </row>
-    <row r="24" ht="36" customHeight="1">
+    <row r="24" ht="66" customHeight="1">
       <c r="A24" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B24" s="48" t="inlineStr">
         <is>
-          <t>Cook until almost dry and sweet-savoury.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C24" s="49" t="n"/>
       <c r="D24" s="49" t="n"/>
     </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Cook until almost dry and sweet-savoury. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 277  ·  Protein 5 g  ·  Carbs 23 g  ·  Fat 19 g  ·  Fibre 5 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Lau Ghonto: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="C20:D20"/>
+  <mergeCells count="31">
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2478,7 +2979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2490,7 +2991,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Luchi</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Luchi</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2500,7 +3001,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>West Bengal kitchen  ·  Bread  ·  Bengali niramish (vegetarian, no onion garlic)</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  West Bengal  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2520,44 +3021,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 20 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -2705,34 +3206,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Fry until they balloon.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Fry until they balloon. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 352  ·  Protein 6 g  ·  Carbs 48 g  ·  Fat 15 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Luchi: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2746,7 +3400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2758,7 +3412,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Radhaballavi</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Radhaballavi</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2768,7 +3422,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>West Bengal kitchen  ·  Bread  ·  Bengali niramish (vegetarian, no onion garlic)</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  West Bengal  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2788,44 +3442,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>Prep 30 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -2991,35 +3645,201 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Stuff, roll, fry in steel.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Steel kadhai for frying — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Stuff, roll, fry in steel. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 362  ·  Protein 16 g  ·  Carbs 71 g  ·  Fat 1 g  ·  Fibre 9 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Radhaballavi: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3033,7 +3853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3045,7 +3865,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Niramish Paratha</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Niramish Paratha</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3055,7 +3875,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>West Bengal kitchen  ·  Bread  ·  Bengali niramish (vegetarian, no onion garlic)</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  West Bengal  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3075,44 +3895,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 20 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -3260,34 +4080,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="54" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Layered paratha on iron tawa.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron tawa (not aluminium). Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Layered paratha on iron tawa. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 318  ·  Protein 9 g  ·  Carbs 54 g  ·  Fat 8 g  ·  Fibre 8 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Niramish Paratha: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3301,7 +4274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3313,7 +4286,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Sandesh</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Sandesh</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3323,7 +4296,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>West Bengal kitchen  ·  Sweet  ·  Bengali niramish (vegetarian, no onion garlic)</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  West Bengal  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3343,44 +4316,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 15 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -3510,33 +4483,186 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Knead, cook lightly in steel, mould.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Knead, cook lightly in steel, mould. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 226  ·  Protein 9 g  ·  Carbs 27 g  ·  Fat 10 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Sandesh: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="26">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3550,7 +4676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3562,7 +4688,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Rasgulla</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Rasgulla</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3572,7 +4698,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>West Bengal kitchen  ·  Sweet  ·  Bengali niramish (vegetarian, no onion garlic)</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  West Bengal  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3592,44 +4718,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 20 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -3759,33 +4885,186 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Boil balls in syrup in a wide steel pot until they sponge.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="66" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Boil balls in syrup in a wide steel pot until they sponge. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 371  ·  Protein 9 g  ·  Carbs 65 g  ·  Fat 10 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Rasgulla: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="26">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3799,7 +5078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3811,7 +5090,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Chomchom</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Chomchom</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3821,7 +5100,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>West Bengal kitchen  ·  Sweet  ·  Bengali niramish (vegetarian, no onion garlic)</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  West Bengal  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3841,44 +5120,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 20 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -4008,33 +5287,186 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Cook like rasgulla, shape ovals, roll.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Cook like rasgulla, shape ovals, roll. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 459  ·  Protein 10 g  ·  Carbs 68 g  ·  Fat 18 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Chomchom: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="26">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4048,7 +5480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4060,7 +5492,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Payesh</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Payesh</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4070,7 +5502,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>West Bengal kitchen  ·  Dessert  ·  Bengali niramish (vegetarian, no onion garlic)</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  West Bengal  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4090,44 +5522,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>Prep 10 min · Cook 40 min</t>
         </is>
       </c>
     </row>
@@ -4293,35 +5725,188 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Simmer in steel until creamy.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Heavy stainless steel milk pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Simmer in steel until creamy. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 438  ·  Protein 12 g  ·  Carbs 77 g  ·  Fat 9 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Payesh: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4599,7 +6184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4611,7 +6196,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Mishti Doi</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Mishti Doi</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4621,7 +6206,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>West Bengal kitchen  ·  Dessert  ·  Bengali niramish (vegetarian, no onion garlic)</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  West Bengal  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4641,44 +6226,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Prep 15 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -4808,33 +6393,199 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Mix, set in clay or glass. Do not set in aluminium.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Clay or glass bowl — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Mix, set in clay or glass. Work in Clay or glass bowl — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Do not set in aluminium. Work in Clay or glass bowl — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 286  ·  Protein 10 g  ·  Carbs 40 g  ·  Fat 11 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Mishti Doi: keep it cold and set before service. Never store yogurt or milk sweets in aluminium. Garnish nuts only if the allergen card allows. Read spice and hing labels if used.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="27">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4848,7 +6599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4860,7 +6611,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Chhanar Payesh</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Chhanar Payesh</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4870,7 +6621,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>West Bengal kitchen  ·  Dessert  ·  Bengali niramish (vegetarian, no onion garlic)</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  West Bengal  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4890,44 +6641,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 15 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -5075,34 +6826,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Simmer chenna in sweet milk in steel.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Heavy stainless steel milk pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Simmer chenna in sweet milk in steel. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 386  ·  Protein 17 g  ·  Carbs 40 g  ·  Fat 19 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Chhanar Payesh: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5116,7 +7020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5128,7 +7032,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Kasundi Cucumber Salad</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Kasundi Cucumber Salad</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5138,7 +7042,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>West Bengal kitchen  ·  Salad  ·  Bengali niramish (vegetarian, no onion garlic)</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  West Bengal  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5158,44 +7062,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>8 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>8 min</t>
+          <t>Prep 8 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -5361,35 +7265,201 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="54" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Toss. Mustard bite instead of onion.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Toss. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Mustard bite instead of onion. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 25  ·  Protein 1 g  ·  Carbs 6 g  ·  Fat 0 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Kasundi Cucumber Salad: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5403,7 +7473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5415,7 +7485,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Tomato Khejur Relish</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Tomato Khejur Relish</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5425,7 +7495,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>West Bengal kitchen  ·  Salad  ·  Bengali niramish (vegetarian, no onion garlic)</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  West Bengal  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5445,44 +7515,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>12 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>22 min</t>
+          <t>Prep 10 min · Cook 12 min</t>
         </is>
       </c>
     </row>
@@ -5684,37 +7754,190 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Cook to a jammy relish.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Cook to a jammy relish. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>kcal 124  ·  Protein 1 g  ·  Carbs 30 g  ·  Fat 1 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="72" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>For Tomato Khejur Relish: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B36" s="52" t="n"/>
+      <c r="C36" s="52" t="n"/>
+      <c r="D36" s="52" t="n"/>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B37" s="50" t="n"/>
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="30">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5728,7 +7951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5740,7 +7963,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Cucumber Lemon Salad</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Cucumber Lemon Salad</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5750,7 +7973,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>West Bengal kitchen  ·  Salad  ·  Bengali niramish (vegetarian, no onion garlic)</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  West Bengal  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5770,44 +7993,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>6 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>6 min</t>
+          <t>Prep 6 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -5973,35 +8196,201 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="54" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Toss. No peyaj.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Toss. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>No peyaj. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 20  ·  Protein 1 g  ·  Carbs 5 g  ·  Fat 0 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Cucumber Lemon Salad: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9375,7 +11764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9387,7 +11776,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Beguni</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Beguni</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9397,7 +11786,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>West Bengal kitchen  ·  Starter  ·  Bengali niramish (vegetarian, no onion garlic)</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  West Bengal  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -9417,44 +11806,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Prep 10 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -9656,37 +12045,190 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Dip, fry in steel until crisp.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Dip, fry in steel until crisp. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>kcal 368  ·  Protein 12 g  ·  Carbs 57 g  ·  Fat 10 g  ·  Fibre 8 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>None identified in this spec — still verify hing brand (many contain wheat) and spice blends.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="72" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>For Beguni: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Cook or roast besan until the raw smell is gone.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B36" s="52" t="n"/>
+      <c r="C36" s="52" t="n"/>
+      <c r="D36" s="52" t="n"/>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: None identified in this spec — still verify hing brand (many contain wheat) and spice blends. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B37" s="50" t="n"/>
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="30">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9700,7 +12242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9712,7 +12254,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Mochar Chop (niramish)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Mochar Chop (niramish)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9722,7 +12264,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>West Bengal kitchen  ·  Starter  ·  Bengali niramish (vegetarian, no onion garlic)</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  West Bengal  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -9742,44 +12284,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 25 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -9999,38 +12541,191 @@
       <c r="C23" s="46" t="n"/>
       <c r="D23" s="46" t="n"/>
     </row>
-    <row r="24" ht="36" customHeight="1">
+    <row r="24" ht="66" customHeight="1">
       <c r="A24" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B24" s="48" t="inlineStr">
         <is>
-          <t>Mash filling, shape, crumb in batter, fry in steel.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C24" s="49" t="n"/>
       <c r="D24" s="49" t="n"/>
     </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. If using potato, cook until tender, drain, and steam-dry so the mix is not wet.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Mash filling, shape, crumb in batter, fry in steel. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 413  ·  Protein 12 g  ·  Carbs 46 g  ·  Fat 21 g  ·  Fibre 9 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>None identified in this spec — still verify hing brand (many contain wheat) and spice blends.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Mochar Chop (niramish): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Cook or roast besan until the raw smell is gone.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: None identified in this spec — still verify hing brand (many contain wheat) and spice blends. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="C20:D20"/>
+  <mergeCells count="31">
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -10044,7 +12739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10056,7 +12751,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Vegetable Chop</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Vegetable Chop</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10066,7 +12761,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>West Bengal kitchen  ·  Starter  ·  Bengali niramish (vegetarian, no onion garlic)</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  West Bengal  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -10086,44 +12781,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 25 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -10325,37 +13020,203 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Mash, shape, fry. Serve with kasundi.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. If using potato, cook until tender, drain, and steam-dry so the mix is not wet.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Mash, shape, fry. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Serve with kasundi. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 360  ·  Protein 13 g  ·  Carbs 51 g  ·  Fat 12 g  ·  Fibre 9 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Vegetable Chop: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Cook or roast besan until the raw smell is gone.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -10369,7 +13230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10381,7 +13242,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Cholar Dal</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Cholar Dal</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10391,7 +13252,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>West Bengal kitchen  ·  Main  ·  Bengali niramish (vegetarian, no onion garlic)</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  West Bengal  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -10411,44 +13272,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 10 min · Cook 30 min</t>
         </is>
       </c>
     </row>
@@ -10668,38 +13529,217 @@
       <c r="C23" s="46" t="n"/>
       <c r="D23" s="46" t="n"/>
     </row>
-    <row r="24" ht="36" customHeight="1">
+    <row r="24" ht="66" customHeight="1">
       <c r="A24" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B24" s="48" t="inlineStr">
         <is>
-          <t>Cook dal. Temper whole spices, coconut, raisins. Slightly sweet.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C24" s="49" t="n"/>
       <c r="D24" s="49" t="n"/>
     </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Cook dal. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Temper whole spices, coconut, raisins. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Slightly sweet. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="31" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="22" t="n"/>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>kcal 252  ·  Protein 6 g  ·  Carbs 21 g  ·  Fat 17 g  ·  Fibre 7 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="48" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="72" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>For Cholar Dal: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B39" s="52" t="n"/>
+      <c r="C39" s="52" t="n"/>
+      <c r="D39" s="52" t="n"/>
+    </row>
+    <row r="40" ht="64" customHeight="1">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B40" s="50" t="n"/>
+      <c r="C40" s="50" t="n"/>
+      <c r="D40" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="C20:D20"/>
+  <mergeCells count="33">
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A33:D33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -10713,7 +13753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10725,7 +13765,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Shukto</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Shukto</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10735,7 +13775,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>West Bengal kitchen  ·  Main  ·  Bengali niramish (vegetarian, no onion garlic)</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  West Bengal  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -10755,44 +13795,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>Prep 20 min · Cook 30 min</t>
         </is>
       </c>
     </row>
@@ -11012,38 +14052,217 @@
       <c r="C23" s="46" t="n"/>
       <c r="D23" s="46" t="n"/>
     </row>
-    <row r="24" ht="42" customHeight="1">
+    <row r="24" ht="66" customHeight="1">
       <c r="A24" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B24" s="48" t="inlineStr">
         <is>
-          <t>Fry bitter gourd first. Cook all veg with paste and milk until creamy. No onion, no garlic.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C24" s="49" t="n"/>
       <c r="D24" s="49" t="n"/>
     </row>
+    <row r="25" ht="66" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. If using potato, cook until tender, drain, and steam-dry so the mix is not wet. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Fry bitter gourd first. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Cook all veg with paste and milk until creamy. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>No onion, no garlic. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="31" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="22" t="n"/>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>kcal 450  ·  Protein 12 g  ·  Carbs 65 g  ·  Fat 17 g  ·  Fibre 4 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="48" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="72" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>For Shukto: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B39" s="52" t="n"/>
+      <c r="C39" s="52" t="n"/>
+      <c r="D39" s="52" t="n"/>
+    </row>
+    <row r="40" ht="64" customHeight="1">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Milk; Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B40" s="50" t="n"/>
+      <c r="C40" s="50" t="n"/>
+      <c r="D40" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="C20:D20"/>
+  <mergeCells count="33">
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A33:D33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -11057,7 +14276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11069,7 +14288,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Dhokar Dalna</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Dhokar Dalna</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11079,7 +14298,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>West Bengal kitchen  ·  Main  ·  Bengali niramish (vegetarian, no onion garlic)</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  West Bengal  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -11099,44 +14318,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>55 min</t>
+          <t>Prep 25 min · Cook 30 min</t>
         </is>
       </c>
     </row>
@@ -11374,36 +14593,215 @@
       <c r="C24" s="46" t="n"/>
       <c r="D24" s="46" t="n"/>
     </row>
-    <row r="25" ht="42" customHeight="1">
+    <row r="25" ht="66" customHeight="1">
       <c r="A25" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B25" s="48" t="inlineStr">
         <is>
-          <t>Make a tomato-ginger gravy in steel. Slide in dhoka pieces. Simmer 8 minutes.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C25" s="49" t="n"/>
       <c r="D25" s="49" t="n"/>
     </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Make a tomato-ginger gravy in steel. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Slide in dhoka pieces. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Simmer 8 minutes. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B31" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C31" s="49" t="n"/>
+      <c r="D31" s="49" t="n"/>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C32" s="31" t="n"/>
+      <c r="D32" s="31" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="n"/>
+      <c r="C34" s="22" t="n"/>
+      <c r="D34" s="22" t="n"/>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>kcal 167  ·  Protein 5 g  ·  Carbs 18 g  ·  Fat 9 g  ·  Fibre 5 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="48" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="26" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+    </row>
+    <row r="39" ht="72" customHeight="1">
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>For Dhokar Dalna: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="n"/>
+      <c r="C39" s="26" t="n"/>
+      <c r="D39" s="26" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B40" s="52" t="n"/>
+      <c r="C40" s="52" t="n"/>
+      <c r="D40" s="52" t="n"/>
+    </row>
+    <row r="41" ht="64" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B41" s="50" t="n"/>
+      <c r="C41" s="50" t="n"/>
+      <c r="D41" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="34">
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
     <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C21:D21"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A41:D41"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="C18:D18"/>
